--- a/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
+++ b/InputData/trans/RTMF/Recipient Transportation Mode Fractions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\RTMF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\trans\RTMF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2643F14-5F7F-4432-8B4A-9A19F1481256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879C9A3C-65AE-46B7-AAAF-3BEC51FB4A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12870" yWindow="1470" windowWidth="22500" windowHeight="21135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>RTMF Recipient Transportation Mode Fractions</t>
   </si>
@@ -138,16 +138,10 @@
     <t>goes to a mix of passenger rail and non-motorized/eliminated</t>
   </si>
   <si>
+    <t>goes to a mix of freight rail and freight ships</t>
+  </si>
+  <si>
     <t>the following mode shifts:</t>
-  </si>
-  <si>
-    <t>freight rail</t>
-  </si>
-  <si>
-    <t>goes to reduced VMT, representing freight logistics</t>
-  </si>
-  <si>
-    <t>goes to reduced VMT, representing lower demand for coal transport</t>
   </si>
 </sst>
 </file>
@@ -214,10 +208,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -238,9 +234,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -278,7 +274,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -384,7 +380,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -526,7 +522,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -534,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
@@ -604,26 +600,30 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
     </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+    </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>29</v>
+      <c r="A25" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
@@ -632,6 +632,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
       <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
@@ -640,19 +641,12 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +660,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -675,7 +669,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -696,7 +690,7 @@
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -704,25 +698,26 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
         <v>0.33</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
         <v>0.33</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6">
         <f>1-SUM(B2:G2)</f>
         <v>0.33999999999999997</v>
       </c>
@@ -731,25 +726,26 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="6">
         <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
         <v>1</v>
       </c>
@@ -758,25 +754,26 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.25</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
@@ -785,25 +782,26 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -812,25 +810,26 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -839,28 +838,38 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -872,7 +881,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.42578125" customWidth="1"/>
@@ -881,7 +890,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -902,7 +911,7 @@
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -910,25 +919,26 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6">
         <f>1-SUM(B2:G2)</f>
         <v>1</v>
       </c>
@@ -937,25 +947,26 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="6">
         <f t="shared" ref="I3:I7" si="0">1-SUM(B3:G3)</f>
         <v>1</v>
       </c>
@@ -964,25 +975,26 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -991,25 +1003,26 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1018,25 +1031,26 @@
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1045,30 +1059,211 @@
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C805E84-6391-4093-8AD7-B2826A68E0C4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86B50622-F5E2-4424-9985-E014F5645E84}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20084E0E-FFBE-4B4F-B8AE-D713884B0EC7}"/>
 </file>